--- a/Result/profitability/1713.xlsx
+++ b/Result/profitability/1713.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.04</v>
       </c>
       <c r="M2" t="n">
-        <v>1.61375</v>
+        <v>1.685</v>
       </c>
       <c r="N2" t="n">
-        <v>7.79125</v>
+        <v>7.325</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.17</v>
       </c>
       <c r="M3" t="n">
-        <v>1.59625</v>
+        <v>0.78875</v>
       </c>
       <c r="N3" t="n">
-        <v>8.077500000000001</v>
+        <v>7.875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>0.68875</v>
+        <v>0.705</v>
       </c>
       <c r="N4" t="n">
-        <v>8.501250000000001</v>
+        <v>9.672499999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.19</v>
       </c>
       <c r="M5" t="n">
-        <v>0.57125</v>
+        <v>0.60375</v>
       </c>
       <c r="N5" t="n">
-        <v>6.985</v>
+        <v>7.12375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>0.49125</v>
+        <v>0.45375</v>
       </c>
       <c r="N6" t="n">
-        <v>6.31625</v>
+        <v>7.121250000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.02</v>
       </c>
       <c r="M7" t="n">
-        <v>0.34625</v>
+        <v>0.2925</v>
       </c>
       <c r="N7" t="n">
-        <v>7.11375</v>
+        <v>7.470000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.05</v>
       </c>
       <c r="M8" t="n">
-        <v>0.18875</v>
+        <v>0.12875</v>
       </c>
       <c r="N8" t="n">
-        <v>8.63625</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>114</v>
+      </c>
+      <c r="D75" t="n">
+        <v>103</v>
+      </c>
+      <c r="E75" t="n">
+        <v>11</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-7.83%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>145</v>
+      </c>
+      <c r="J75" t="n">
+        <v>136</v>
+      </c>
+      <c r="K75" t="n">
+        <v>133</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.71875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>7.72375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.4800000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3529411764705883</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.8499999999999996</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.08276533592989288</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4193548387096775</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.109999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1335740072202165</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
